--- a/inspection_forms/005_drone_surveillance_equipment_inspection_form--inspection_forms.xlsx
+++ b/inspection_forms/005_drone_surveillance_equipment_inspection_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>equipment_condition</t>
+          <t>equipment_condition_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Equipment Condition</t>
+          <t>Equipment Condition 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maintenance_record</t>
+          <t>maintenance_record_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Maintenance Record</t>
+          <t>Maintenance Record 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>certification_expiration_date</t>
+          <t>certification_expiration_date_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Certification Expiration Date</t>
+          <t>Certification Expiration Date 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
